--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=30_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=30_without_41.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9462991255282774</v>
+        <v>0.9462991255282771</v>
       </c>
       <c r="C3" t="n">
-        <v>1.652492887293147</v>
+        <v>1.652492887293145</v>
       </c>
       <c r="D3" t="n">
         <v>1.8</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9564615828171127</v>
+        <v>0.9564615828171125</v>
       </c>
       <c r="C4" t="n">
-        <v>1.896094392796249</v>
+        <v>1.89609439279625</v>
       </c>
       <c r="D4" t="n">
         <v>2.05</v>
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9460673212852195</v>
+        <v>0.9460673212852198</v>
       </c>
       <c r="C5" t="n">
         <v>2.195476295175628</v>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9301612847842107</v>
+        <v>0.9301612847842105</v>
       </c>
       <c r="C6" t="n">
         <v>2.032319400203713</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6120657751304872</v>
+        <v>0.91344981604854</v>
       </c>
       <c r="C7" t="n">
-        <v>1.593623690058529</v>
+        <v>1.564834725725462</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9777733605690189</v>
+        <v>0.9456924895013725</v>
       </c>
       <c r="C8" t="n">
-        <v>1.928659199116467</v>
+        <v>1.988613570994308</v>
       </c>
       <c r="D8" t="n">
         <v>2.52</v>
@@ -567,7 +567,7 @@
         <v>0.9457997029318452</v>
       </c>
       <c r="C9" t="n">
-        <v>2.909257128941863</v>
+        <v>2.909257128941866</v>
       </c>
       <c r="D9" t="n">
         <v>2.25</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9336628074744417</v>
+        <v>0.9336628074744415</v>
       </c>
       <c r="C10" t="n">
-        <v>1.593769547660082</v>
+        <v>1.593769547660083</v>
       </c>
       <c r="D10" t="n">
         <v>1.75</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9121139869065893</v>
+        <v>0.912113986906589</v>
       </c>
       <c r="C13" t="n">
         <v>1.556345199464247</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9193864722484817</v>
+        <v>0.9193864722484825</v>
       </c>
       <c r="C14" t="n">
         <v>1.442971511282391</v>
@@ -663,7 +663,7 @@
         <v>0.8358527600771796</v>
       </c>
       <c r="C15" t="n">
-        <v>1.595417850252569</v>
+        <v>1.595417850252567</v>
       </c>
       <c r="D15" t="n">
         <v>1.5</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9174147801004296</v>
+        <v>0.9174147801004303</v>
       </c>
       <c r="C16" t="n">
         <v>1.337145587960421</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7480387660677363</v>
+        <v>0.7480387660677361</v>
       </c>
       <c r="C17" t="n">
-        <v>2.82818752061558</v>
+        <v>2.828187520615586</v>
       </c>
       <c r="D17" t="n">
         <v>2.8</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9458629137499454</v>
+        <v>0.848583877941115</v>
       </c>
       <c r="C18" t="n">
-        <v>2.490650469319557</v>
+        <v>2.578306965775575</v>
       </c>
       <c r="D18" t="n">
         <v>1.95</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9119447648315009</v>
+        <v>0.9119447648315011</v>
       </c>
       <c r="C19" t="n">
         <v>1.632012528888971</v>
